--- a/temp/MACRO_VISA_20250610.xlsx
+++ b/temp/MACRO_VISA_20250610.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>

--- a/temp/MACRO_VISA_20250610.xlsx
+++ b/temp/MACRO_VISA_20250610.xlsx
@@ -471,12 +471,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-2526.56</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-2526,56</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>18675</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18675,0</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>27640</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>27640,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>21732</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21732,0</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>900</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>900,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>950</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>950,0</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>950</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>950,0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>14400</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>14400,0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -671,12 +687,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>7500</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7500,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>5100</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5100,0</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>53700</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>53700,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>18000</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>18000,0</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>23270</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>23270,0</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>

--- a/temp/MACRO_VISA_20250610.xlsx
+++ b/temp/MACRO_VISA_20250610.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>006178K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>006160K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>006254K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>006145K PEDIDOSYA*PROPINA</t>
+          <t>PEDIDOSYA*PROPINA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>006288K PEDIDOSYA*PROPINA</t>
+          <t>PEDIDOSYA*PROPINA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>006088K PEDIDOSYA*PROPINA</t>
+          <t>PEDIDOSYA*PROPINA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>146778K MERPAGO*HACIENDACOFFE</t>
+          <t>MERPAGO*HACIENDACOFFE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>343895K MERPAGO*HACIENDACOFFE</t>
+          <t>MERPAGO*HACIENDACOFFE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>067055K MERPAGO*MCDONALDS</t>
+          <t>MERPAGO*MCDONALDS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>055298K MERPAGO*BANDOLBELGRAN</t>
+          <t>MERPAGO*BANDOLBELGRAN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>261112K MERPAGO*VILLACRESPO</t>
+          <t>MERPAGO*VILLACRESPO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>343136* MERPAGO*REUSCH Cuota 01/03</t>
+          <t>MERPAGO*REUSCH Cuota 01/03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
